--- a/data sources/detailed material intensity source.xlsx
+++ b/data sources/detailed material intensity source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marita/Documents/GitHub/MFA2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marita/Documents/GitHub/MFA2/data sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{77D661ED-BAA8-D243-82AF-8F3ED6F625C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="9" r:id="rId1"/>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -350,54 +350,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -818,6 +788,35 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -898,15 +897,21 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
         </left>
         <right style="thin">
           <color auto="1"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -927,21 +932,15 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
         <right style="thin">
           <color auto="1"/>
         </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -958,7 +957,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3823403C-C8A7-D84F-AC95-93A1F973CB80}" name="Tabell1" displayName="Tabell1" ref="A1:E386" totalsRowCount="1" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3823403C-C8A7-D84F-AC95-93A1F973CB80}" name="Tabell1" displayName="Tabell1" ref="A1:E386" totalsRowCount="1" headerRowDxfId="20">
   <autoFilter ref="A1:E385" xr:uid="{3823403C-C8A7-D84F-AC95-93A1F973CB80}">
     <filterColumn colId="3">
       <filters>
@@ -970,7 +969,7 @@
     <sortCondition ref="B1:B385"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{05906E75-D7DD-9143-BF33-6972AFA7FB75}" name="Kolonne1" dataDxfId="20" totalsRowDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{05906E75-D7DD-9143-BF33-6972AFA7FB75}" name="Kolonne1" dataDxfId="19" totalsRowDxfId="18"/>
     <tableColumn id="2" xr3:uid="{4B60E661-120B-7A40-8DB0-931DE8A229C5}" name="function" totalsRowDxfId="17"/>
     <tableColumn id="3" xr3:uid="{61F44892-8F35-E640-B218-2C6279DCE134}" name="structure" totalsRowDxfId="16"/>
     <tableColumn id="4" xr3:uid="{B2B09C76-9A2B-5E47-B2DA-4A0851FE3C85}" name="R5_32" totalsRowDxfId="15"/>
@@ -981,7 +980,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92255858-791D-F144-B233-B7E34FD0D5A2}" name="Tabell2" displayName="Tabell2" ref="A1:E385" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92255858-791D-F144-B233-B7E34FD0D5A2}" name="Tabell2" displayName="Tabell2" ref="A1:E385" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:E385" xr:uid="{92255858-791D-F144-B233-B7E34FD0D5A2}">
     <filterColumn colId="1">
       <filters>
@@ -996,7 +995,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{73DB6E78-AA67-1244-8D29-BBC29E59BEA6}" name="Kolonne1" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{73DB6E78-AA67-1244-8D29-BBC29E59BEA6}" name="Kolonne1" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{C15CA2BA-0E5B-3044-862D-28AC9D0F7098}" name="function"/>
     <tableColumn id="3" xr3:uid="{E919CB76-9241-534C-9C78-1A68773104D9}" name="structure"/>
     <tableColumn id="4" xr3:uid="{5F0AAB27-2885-2643-8194-0613FB69A2EF}" name="R5_32"/>
@@ -1007,7 +1006,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6FAD8103-BB69-1A48-9AB2-A7B9DAC4C601}" name="Tabell3" displayName="Tabell3" ref="A1:E385" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6FAD8103-BB69-1A48-9AB2-A7B9DAC4C601}" name="Tabell3" displayName="Tabell3" ref="A1:E385" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A1:E385" xr:uid="{6FAD8103-BB69-1A48-9AB2-A7B9DAC4C601}">
     <filterColumn colId="1">
       <filters>
@@ -1022,7 +1021,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{30D3D312-7F48-ED4A-84CA-9C4D9D6F9B2A}" name="Kolonne1" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{30D3D312-7F48-ED4A-84CA-9C4D9D6F9B2A}" name="Kolonne1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{FB363CA2-3962-B441-91F4-88763F300DDE}" name="function"/>
     <tableColumn id="3" xr3:uid="{76F20789-7138-A545-9F4B-27DD01592387}" name="structure"/>
     <tableColumn id="4" xr3:uid="{7E0A94EA-C8D0-4448-821B-377D66946EF8}" name="R5_32"/>
@@ -1033,7 +1032,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0F1121C5-3B36-2149-980A-09CC5C9F4B3B}" name="Tabell4" displayName="Tabell4" ref="A1:E385" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0F1121C5-3B36-2149-980A-09CC5C9F4B3B}" name="Tabell4" displayName="Tabell4" ref="A1:E385" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:E385" xr:uid="{0F1121C5-3B36-2149-980A-09CC5C9F4B3B}">
     <filterColumn colId="1">
       <filters>
@@ -1048,7 +1047,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F8DECE1B-21C1-B142-8CB0-CD2425A1C011}" name="Kolonne1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{F8DECE1B-21C1-B142-8CB0-CD2425A1C011}" name="Kolonne1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{0AF34D79-E4D1-0E4E-A1BB-468CA9667575}" name="function"/>
     <tableColumn id="3" xr3:uid="{0BD0DE31-AC38-AA43-836C-E2AD61B2802A}" name="structure"/>
     <tableColumn id="4" xr3:uid="{35D64403-130A-3840-82F9-D7539D0AA088}" name="R5_32"/>
@@ -1059,7 +1058,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A2EBDD27-48E0-864D-9376-FA91423B16A2}" name="Tabell5" displayName="Tabell5" ref="A1:E385" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A2EBDD27-48E0-864D-9376-FA91423B16A2}" name="Tabell5" displayName="Tabell5" ref="A1:E385" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:E385" xr:uid="{A2EBDD27-48E0-864D-9376-FA91423B16A2}">
     <filterColumn colId="1">
       <filters>
@@ -1074,7 +1073,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{87FC9302-CE94-FB40-91FE-FD9D1C1CCE1D}" name="Kolonne1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{87FC9302-CE94-FB40-91FE-FD9D1C1CCE1D}" name="Kolonne1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{C3C9A313-8092-674E-A8E7-BE192BA61F53}" name="function"/>
     <tableColumn id="3" xr3:uid="{D5E054DC-C7EB-B749-943B-F56CDB05CAA8}" name="structure"/>
     <tableColumn id="4" xr3:uid="{81D25F65-B3BC-644B-A44A-8339175C8F25}" name="R5_32"/>
@@ -1085,7 +1084,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8535E957-3C6F-3548-9D3C-66CD610D1761}" name="Tabell6" displayName="Tabell6" ref="A1:E385" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8535E957-3C6F-3548-9D3C-66CD610D1761}" name="Tabell6" displayName="Tabell6" ref="A1:E385" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:E385" xr:uid="{8535E957-3C6F-3548-9D3C-66CD610D1761}">
     <filterColumn colId="1">
       <filters>
@@ -1100,7 +1099,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{43FBB5BA-8374-D246-9580-964611B49C40}" name="Kolonne1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{43FBB5BA-8374-D246-9580-964611B49C40}" name="Kolonne1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{8EEAE5D8-43A2-224F-B854-EF51FFCCF440}" name="function"/>
     <tableColumn id="3" xr3:uid="{1693C665-AEA9-F94C-9F19-0222CDF14366}" name="structure"/>
     <tableColumn id="4" xr3:uid="{B7388CF0-1543-004F-BFFE-6A6C60FA891D}" name="R5_32"/>
@@ -1111,7 +1110,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6ADF6BD8-4AC8-5948-9970-BFB5ADA6C7E9}" name="Tabell7" displayName="Tabell7" ref="A1:E385" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6ADF6BD8-4AC8-5948-9970-BFB5ADA6C7E9}" name="Tabell7" displayName="Tabell7" ref="A1:E385" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:E385" xr:uid="{6ADF6BD8-4AC8-5948-9970-BFB5ADA6C7E9}">
     <filterColumn colId="1">
       <filters>
@@ -1126,7 +1125,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EC324037-5055-C147-8C38-A58EDFAF47B3}" name="Kolonne1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{EC324037-5055-C147-8C38-A58EDFAF47B3}" name="Kolonne1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{1DFF3596-23E7-6240-B6CB-9025B3602171}" name="function"/>
     <tableColumn id="3" xr3:uid="{03D389DB-AFAE-904B-A7B2-9564006A9749}" name="structure"/>
     <tableColumn id="4" xr3:uid="{42181789-5675-4548-92DF-038F90D26C78}" name="R5_32"/>
@@ -1137,7 +1136,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5B42C9A3-6CFF-1840-B228-95158482A84C}" name="Tabell8" displayName="Tabell8" ref="A1:E385" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5B42C9A3-6CFF-1840-B228-95158482A84C}" name="Tabell8" displayName="Tabell8" ref="A1:E385" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:E385" xr:uid="{5B42C9A3-6CFF-1840-B228-95158482A84C}">
     <filterColumn colId="1">
       <filters>
@@ -1152,7 +1151,7 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{92BD136D-E72C-0E4D-A3CE-41BCEEDA871D}" name="Kolonne1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{92BD136D-E72C-0E4D-A3CE-41BCEEDA871D}" name="Kolonne1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{8FC177F6-BDBC-AC45-A1C8-4AEC5DFE6BA3}" name="function"/>
     <tableColumn id="3" xr3:uid="{883AFF99-3558-D648-A400-57443DF0157F}" name="structure"/>
     <tableColumn id="4" xr3:uid="{8C0D47E7-33F7-0F4D-8504-11E13F73240E}" name="R5_32"/>
@@ -1451,329 +1450,329 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="14">
+      <c r="A2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="13">
         <v>932.54475703324806</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>268.75</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>9.8974358974999994</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>52.60229133</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>3.1</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <v>1.2202600185000001</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>0.496117796</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K2" s="10">
-        <f>SUM(C2:J2)</f>
+      <c r="K2" s="9">
+        <f t="shared" ref="K2:K9" si="0">SUM(C2:J2)</f>
         <v>1268.7937575702479</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="A3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="15">
         <v>867.15639810000005</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <v>181.38599195</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <v>20.284360190000001</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <v>32.450000000000003</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <v>2.1</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>1.322689139</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>0.48685159049999999</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K3" s="10">
-        <f>SUM(C3:J3)</f>
+      <c r="K3" s="9">
+        <f t="shared" si="0"/>
         <v>1105.3691864644998</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="18">
+      <c r="A4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="17">
         <v>238</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>639.51327430000003</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>53.235677083333343</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>21.653209104999998</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="17">
         <v>2</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <v>1.1994062379999999</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="17">
         <v>0.49</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="17">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K4" s="10">
-        <f>SUM(C4:J4)</f>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
         <v>956.27446222133347</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="16">
+      <c r="A5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="15">
         <v>621.00108935000003</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>693.33333333333337</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>20.304568530000001</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>36.209777777777781</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>1.6008487309999999</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>1.1994062379999999</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="15">
         <v>0.49305889800000002</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="15">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K5" s="10">
-        <f>SUM(C5:J5)</f>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
         <v>1374.3249783531112</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="A6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="17">
         <v>534.98385359999997</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>32.666666669999998</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>22</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>70.5</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>2.65</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>1.1994062379999999</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="17">
         <v>0.49</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="17">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K6" s="10">
-        <f>SUM(C6:J6)</f>
+      <c r="K6" s="9">
+        <f t="shared" si="0"/>
         <v>664.67282200300008</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="16">
+      <c r="A7" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="15">
         <v>584</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>32.666666669999998</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>20</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>125</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>2</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>1.1994062379999999</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0.49</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K7" s="10">
-        <f>SUM(C7:J7)</f>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
         <v>765.53896840300013</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="A8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="17">
         <v>218.5</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>89</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>149</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>17.5023432652075</v>
       </c>
-      <c r="G8" s="18">
-        <v>4</v>
-      </c>
-      <c r="H8" s="18">
+      <c r="G8" s="17">
+        <v>4</v>
+      </c>
+      <c r="H8" s="17">
         <v>1.1896697199999999</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <v>0.49</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="17">
         <v>0.18289549499999999</v>
       </c>
-      <c r="K8" s="10">
-        <f>SUM(C8:J8)</f>
+      <c r="K8" s="9">
+        <f t="shared" si="0"/>
         <v>479.86490848020753</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="A9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="15">
         <v>343</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>34</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>110.2518518518519</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>34.09411764705883</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <v>2.4425941980000001</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>1.2091427560000001</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <v>0.49</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <v>0.18824956900000001</v>
       </c>
-      <c r="K9" s="10">
-        <f>SUM(C9:J9)</f>
+      <c r="K9" s="9">
+        <f t="shared" si="0"/>
         <v>525.67595602191079</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -5512,7 +5511,7 @@
       <c r="D222" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E222" s="8">
+      <c r="E222" s="7">
         <v>932.54475703324806</v>
       </c>
     </row>
@@ -5886,7 +5885,7 @@
       <c r="D244" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E244" s="8">
+      <c r="E244" s="7">
         <v>238</v>
       </c>
     </row>
@@ -5903,7 +5902,7 @@
       <c r="D245" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E245" s="8">
+      <c r="E245" s="7">
         <v>534.98385359999997</v>
       </c>
     </row>
@@ -5920,7 +5919,7 @@
       <c r="D246" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E246" s="8">
+      <c r="E246" s="7">
         <v>218.5</v>
       </c>
     </row>
@@ -5937,7 +5936,7 @@
       <c r="D247" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E247" s="9">
+      <c r="E247" s="8">
         <v>867.15639810000005</v>
       </c>
     </row>
@@ -5954,7 +5953,7 @@
       <c r="D248" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E248" s="9">
+      <c r="E248" s="8">
         <v>621.00108935000003</v>
       </c>
     </row>
@@ -5971,7 +5970,7 @@
       <c r="D249" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E249" s="9">
+      <c r="E249" s="8">
         <v>584</v>
       </c>
     </row>
@@ -5988,7 +5987,7 @@
       <c r="D250" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="9">
+      <c r="E250" s="8">
         <v>343</v>
       </c>
     </row>
@@ -8289,10 +8288,6 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" s="6"/>
-      <c r="B386" s="7"/>
-      <c r="C386" s="7"/>
-      <c r="D386" s="7"/>
-      <c r="E386" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17491,7 +17486,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>9.8974358974999994</v>
       </c>
     </row>
@@ -18035,7 +18030,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>53.235677083333343</v>
       </c>
     </row>
@@ -18579,7 +18574,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>22</v>
       </c>
     </row>
@@ -19123,7 +19118,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>149</v>
       </c>
     </row>
@@ -19667,7 +19662,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>20.284360190000001</v>
       </c>
     </row>
@@ -20211,7 +20206,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>20.304568530000001</v>
       </c>
     </row>
@@ -20755,7 +20750,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>20</v>
       </c>
     </row>
@@ -21299,7 +21294,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>110.2518518518519</v>
       </c>
     </row>
@@ -24055,7 +24050,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>52.60229133</v>
       </c>
     </row>
@@ -24599,7 +24594,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>21.653209104999998</v>
       </c>
     </row>
@@ -25143,7 +25138,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>70.5</v>
       </c>
     </row>
@@ -25687,7 +25682,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>17.5023432652075</v>
       </c>
     </row>
@@ -26231,7 +26226,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>32.450000000000003</v>
       </c>
     </row>
@@ -26775,7 +26770,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>36.209777777777781</v>
       </c>
     </row>
@@ -27319,7 +27314,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>125</v>
       </c>
     </row>
@@ -27863,7 +27858,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>34.09411764705883</v>
       </c>
     </row>
@@ -30619,7 +30614,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>3.1</v>
       </c>
     </row>
@@ -31163,7 +31158,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>2</v>
       </c>
     </row>
@@ -31707,7 +31702,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>2.65</v>
       </c>
     </row>
@@ -32251,7 +32246,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>4</v>
       </c>
     </row>
@@ -32795,7 +32790,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>2.1</v>
       </c>
     </row>
@@ -33339,7 +33334,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>1.6008487309999999</v>
       </c>
     </row>
@@ -33883,7 +33878,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>2</v>
       </c>
     </row>
@@ -34427,7 +34422,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>2.4425941980000001</v>
       </c>
     </row>
@@ -37183,7 +37178,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>1.2202600185000001</v>
       </c>
     </row>
@@ -37727,7 +37722,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>1.1994062379999999</v>
       </c>
     </row>
@@ -38271,7 +38266,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>1.1994062379999999</v>
       </c>
     </row>
@@ -38815,7 +38810,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>1.1896697199999999</v>
       </c>
     </row>
@@ -39359,7 +39354,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>1.322689139</v>
       </c>
     </row>
@@ -39903,7 +39898,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>1.1994062379999999</v>
       </c>
     </row>
@@ -40447,7 +40442,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>1.1994062379999999</v>
       </c>
     </row>
@@ -40991,7 +40986,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>1.2091427560000001</v>
       </c>
     </row>
@@ -43746,7 +43741,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>0.496117796</v>
       </c>
     </row>
@@ -44290,7 +44285,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>0.49</v>
       </c>
     </row>
@@ -44834,7 +44829,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>0.49</v>
       </c>
     </row>
@@ -45378,7 +45373,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>0.49</v>
       </c>
     </row>
@@ -45922,7 +45917,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>0.48685159049999999</v>
       </c>
     </row>
@@ -46466,7 +46461,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>0.49305889800000002</v>
       </c>
     </row>
@@ -47010,7 +47005,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>0.49</v>
       </c>
     </row>
@@ -47554,7 +47549,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>0.49</v>
       </c>
     </row>
@@ -50310,7 +50305,7 @@
       <c r="D154" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="7">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -50854,7 +50849,7 @@
       <c r="D186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -51398,7 +51393,7 @@
       <c r="D218" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="7">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -51942,7 +51937,7 @@
       <c r="D250" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="7">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -52486,7 +52481,7 @@
       <c r="D282" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E282" s="9">
+      <c r="E282" s="8">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -53030,7 +53025,7 @@
       <c r="D314" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E314" s="9">
+      <c r="E314" s="8">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -53574,7 +53569,7 @@
       <c r="D346" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E346" s="9">
+      <c r="E346" s="8">
         <v>0.18289549499999999</v>
       </c>
     </row>
@@ -54118,7 +54113,7 @@
       <c r="D378" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E378" s="9">
+      <c r="E378" s="8">
         <v>0.18824956900000001</v>
       </c>
     </row>
@@ -54242,7 +54237,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E386" s="10"/>
+      <c r="E386" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
